--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -877,6 +877,112 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129842127</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102168</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1660</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Luddvicker</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Vicia villosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Roth</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Jägarvallsrondellen NNO, 200 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>532367</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6473582</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Slaka</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>E-Lin-0137</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129842127</v>
       </c>
       <c r="B4" t="n">
-        <v>102168</v>
+        <v>102172</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129842127</v>
       </c>
       <c r="B4" t="n">
-        <v>102172</v>
+        <v>102174</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129842127</v>
       </c>
       <c r="B4" t="n">
-        <v>102174</v>
+        <v>102184</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129842127</v>
       </c>
       <c r="B4" t="n">
-        <v>102184</v>
+        <v>102188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129842127</v>
       </c>
       <c r="B4" t="n">
-        <v>102188</v>
+        <v>102191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129842127</v>
       </c>
       <c r="B4" t="n">
-        <v>102191</v>
+        <v>102192</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129842127</v>
       </c>
       <c r="B4" t="n">
-        <v>102192</v>
+        <v>102209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129842127</v>
       </c>
       <c r="B4" t="n">
-        <v>102225</v>
+        <v>102227</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129842127</v>
       </c>
       <c r="B4" t="n">
-        <v>102227</v>
+        <v>102314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129842127</v>
       </c>
       <c r="B4" t="n">
-        <v>102431</v>
+        <v>102432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129842127</v>
       </c>
       <c r="B4" t="n">
-        <v>102432</v>
+        <v>102435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129842127</v>
       </c>
       <c r="B4" t="n">
-        <v>102435</v>
+        <v>102439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129842127</v>
       </c>
       <c r="B4" t="n">
-        <v>102439</v>
+        <v>102438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129842127</v>
       </c>
       <c r="B4" t="n">
-        <v>102438</v>
+        <v>102439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129842127</v>
       </c>
       <c r="B4" t="n">
-        <v>102439</v>
+        <v>102440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129842127</v>
       </c>
       <c r="B4" t="n">
-        <v>102440</v>
+        <v>102443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129842127</v>
       </c>
       <c r="B4" t="n">
-        <v>102443</v>
+        <v>102448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129842127</v>
       </c>
       <c r="B4" t="n">
-        <v>102448</v>
+        <v>102454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122288265</v>
+        <v>432451</v>
       </c>
       <c r="B2" t="n">
-        <v>44595</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102019</v>
+        <v>1660</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klubbsprötad bastardsvärmare</t>
+          <t>Luddvicker</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zygaena minos</t>
+          <t>Vicia villosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>Roth</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nya Kalmarvägen, Ög</t>
+          <t>Jägarvallsrondellen NNO, 200 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532358</v>
+        <v>532367</v>
       </c>
       <c r="R2" t="n">
-        <v>6473562</v>
+        <v>6473582</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,14 +738,24 @@
           <t>Slaka</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>E-Lin-0137</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>1990-06-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>1990-06-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>X ba 45F</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,31 +770,30 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>E-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Bo Antberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122288266</v>
+        <v>434704</v>
       </c>
       <c r="B3" t="n">
-        <v>101712</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -810,20 +814,24 @@
           <t>Roth</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nya Kalmarvägen, Ög</t>
+          <t>Jägarvallsrondellen SV, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532364</v>
+        <v>532267</v>
       </c>
       <c r="R3" t="n">
-        <v>6473574</v>
+        <v>6473446</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -845,14 +853,24 @@
           <t>Slaka</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>E-Lin-0136</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>1996-06-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>1996-06-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 ex, tj 45E</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,26 +885,30 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>E-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129842127</v>
+        <v>122288266</v>
       </c>
       <c r="B4" t="n">
-        <v>102454</v>
+        <v>102542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -910,17 +932,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jägarvallsrondellen NNO, 200 m, Ög</t>
+          <t>Nya Kalmarvägen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532367</v>
+        <v>532364</v>
       </c>
       <c r="R4" t="n">
-        <v>6473582</v>
+        <v>6473574</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -940,11 +962,6 @@
       <c r="W4" t="inlineStr">
         <is>
           <t>Slaka</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>E-Lin-0137</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -969,7 +986,7 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Monika Sunhede</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -977,11 +994,201 @@
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122288264</v>
+      </c>
+      <c r="B5" t="n">
+        <v>45045</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102019</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Klubbsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Zygaena minos</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nya Kalmarvägen, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>532273</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6473451</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Slaka</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122288265</v>
+      </c>
+      <c r="B6" t="n">
+        <v>45045</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102019</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Klubbsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Zygaena minos</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nya Kalmarvägen, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>532358</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6473562</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Slaka</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8818-2025 artfynd.xlsx
+++ b/artfynd/A 8818-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/432451</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/434704</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122288266</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122288264</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,8 +1214,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122288265</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>